--- a/demo/output_reports/TAPD缺陷报告_UIKit3.1版本_各处理人负责缺陷数.xlsx
+++ b/demo/output_reports/TAPD缺陷报告_UIKit3.1版本_各处理人负责缺陷数.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>【LiveKit-3.1版本】【freetest】【Android】【直播】安卓端主播和其他主播PK，PK过程中，打开悬浮窗，然后回到直播间，PK进度条样式错误</t>
+          <t>【LiveKit-3.1版本】【freetest】【Android】【直播】【新引入】安卓端主播和其他主播PK，PK过程中，打开悬浮窗，然后回到直播间，PK进度条样式错误</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>【LiveKit-3.1版本】【系统测试】【集中测试】【IOS】IOS端房主，直播间只要有连麦观众，底部的连麦按钮会一直闪烁，连麦观众下麦后，恢复正常</t>
+          <t>【LiveKit-3.1版本】【系统测试】【集中测试】【IOS】【实际非重新打开】IOS端房主，直播间只要有连麦观众，底部的连麦按钮会一直闪烁，连麦观众下麦后，恢复正常</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>【RoomKit-3.1版本】【系统测试】【集中测试】【flutter】【Android】#4构建，偶现用户静音按钮与手机实际效果不符</t>
+          <t>【RoomKit-3.1版本】【系统测试】【集中测试】【flutter】【Android】#4构建，用户静音按钮与手机实际效果不符</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>【LiveKit-3.1版本】【需求测试】【LiveKit弱网场景测试】【IOS】观众进房后，画面黑屏，音频正常，</t>
+          <t>【LiveKit-3.1版本】【需求测试】【LiveKit弱网场景测试】【IOS】【实际非重新打开】观众进房后，画面黑屏，音频正常，</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
